--- a/data/trending_integrated_20260916_12.xlsx
+++ b/data/trending_integrated_20260916_12.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F2" t="n">
         <v>143</v>
       </c>
       <c r="G2" t="n">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7203396930</v>
+        <v>7383857730</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 미투온 인수 관련 카지노 사업 진출 기대감. 클래리티법 부결 영향 미미. 숏커버링 발생 및 미버스코인 급등.</t>
+          <t>카카오 인수 관련하여 합법 카지노 사업 확장 기대감이 높으나, 인수 조건 및 시총 관련 분석은 미흡. 공매도 숏스퀴즈 발생 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오 인수', '카지노', '숏커버링']</t>
+          <t>['카카오 인수', '카지노', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13620</v>
+        <v>13610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.29%</t>
+          <t>'+27.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>167269771220</v>
+        <v>168301490000</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16200</v>
+        <v>16320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.57%</t>
+          <t>'+15.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F4" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G4" t="n">
-        <v>1265</v>
+        <v>1308</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>469969341355</v>
+        <v>485534431040</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대규모 매집 및 프로그램 매수세 유입, 1.6만원 돌파 및 우상향 추세 전망.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 285건 토론 포착</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['매집', '프로그램', '우상향']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4530</v>
+        <v>4535</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.95%</t>
+          <t>'+10.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
         <v>158</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>287577517279</v>
+        <v>289696176098</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3765</v>
+        <v>3730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.11%</t>
+          <t>'+6.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>15521378369</v>
+        <v>15660865813</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 108건 토론 포착</t>
+          <t>재탕 뉴스에 기반한 상승 기대감과 달리, 상당한 규모의 적자 지속으로 인한 상폐 가능성 및 주가 하락 전망 제기. 투자자 주의 요구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['적자', '상폐', '재탕 뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3520</v>
+        <v>7200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.76%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.34</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,139 +1055,139 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3360</v>
+        <v>6900</v>
       </c>
       <c r="K7" t="n">
-        <v>3570</v>
+        <v>6770</v>
       </c>
       <c r="L7" t="n">
-        <v>3910</v>
+        <v>8590</v>
       </c>
       <c r="M7" t="n">
-        <v>3345</v>
+        <v>6660</v>
       </c>
       <c r="N7" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>94885944901</v>
+        <v>73745200210</v>
       </c>
       <c r="P7" t="n">
-        <v>5100</v>
+        <v>10360</v>
       </c>
       <c r="Q7" t="n">
-        <v>966</v>
+        <v>2965</v>
       </c>
       <c r="R7" t="n">
-        <v>9000</v>
+        <v>87000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>양자암호 해독키 독점 공급 및 미국 보안주 상승 수혜, 가벼운 종목으로 빠른 상승 기대.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '매집']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10520</v>
+        <v>3470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10120</v>
+        <v>3360</v>
       </c>
       <c r="K8" t="n">
-        <v>10190</v>
+        <v>3570</v>
       </c>
       <c r="L8" t="n">
-        <v>10920</v>
+        <v>3910</v>
       </c>
       <c r="M8" t="n">
-        <v>9790</v>
+        <v>3345</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>101785644010</v>
+        <v>95694375397</v>
       </c>
       <c r="P8" t="n">
-        <v>15960</v>
+        <v>5100</v>
       </c>
       <c r="Q8" t="n">
-        <v>3500</v>
+        <v>966</v>
       </c>
       <c r="R8" t="n">
-        <v>-9000</v>
+        <v>9000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미프진 도입 공식화 관련 재료 소멸 및 주가 하락 우려, 단기 반등 기대.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 82건 토론 포착</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '주가조작']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7130</v>
+        <v>192900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.33%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
         <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>51</v>
+        <v>242</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>75.66</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6900</v>
+        <v>187100</v>
       </c>
       <c r="K9" t="n">
-        <v>6770</v>
+        <v>187200</v>
       </c>
       <c r="L9" t="n">
-        <v>8590</v>
+        <v>195900</v>
       </c>
       <c r="M9" t="n">
-        <v>6660</v>
+        <v>186100</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>73495978990</v>
+        <v>407500031750</v>
       </c>
       <c r="P9" t="n">
-        <v>10360</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>2965</v>
+        <v>61800</v>
       </c>
       <c r="R9" t="n">
-        <v>87000</v>
+        <v>21000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192600</v>
+        <v>1727000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.94%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>480</v>
       </c>
       <c r="G10" t="n">
-        <v>238</v>
+        <v>1847</v>
       </c>
       <c r="H10" t="n">
-        <v>75.66</v>
+        <v>50.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>187100</v>
+        <v>1690000</v>
       </c>
       <c r="K10" t="n">
-        <v>187200</v>
+        <v>1686000</v>
       </c>
       <c r="L10" t="n">
-        <v>195900</v>
+        <v>1731000</v>
       </c>
       <c r="M10" t="n">
-        <v>186100</v>
+        <v>1686000</v>
       </c>
       <c r="N10" t="n">
-        <v>75.67</v>
+        <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>398011043050</v>
+        <v>2187352077000</v>
       </c>
       <c r="P10" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>61800</v>
+        <v>331500</v>
       </c>
       <c r="R10" t="n">
-        <v>21000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 800건 토론 포착</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,51 +1371,51 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1725000</v>
+        <v>10310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+1.88%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>108</v>
       </c>
       <c r="F11" t="n">
-        <v>484</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>1905</v>
+        <v>228</v>
       </c>
       <c r="H11" t="n">
-        <v>50.2</v>
+        <v>0.67</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1690000</v>
+        <v>10120</v>
       </c>
       <c r="K11" t="n">
-        <v>1686000</v>
+        <v>10190</v>
       </c>
       <c r="L11" t="n">
-        <v>1731000</v>
+        <v>10920</v>
       </c>
       <c r="M11" t="n">
-        <v>1686000</v>
+        <v>9790</v>
       </c>
       <c r="N11" t="n">
-        <v>50.27</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2076399149500</v>
+        <v>105403113090</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>15960</v>
       </c>
       <c r="Q11" t="n">
-        <v>331500</v>
+        <v>3500</v>
       </c>
       <c r="R11" t="n">
-        <v>-12000</v>
+        <v>-9000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감 속 주가 상승, 반도체 실적 발표 시즌 언급.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 108건 토론 포착</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주', '반도체', '실적']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252000</v>
+        <v>252500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G12" t="n">
-        <v>1817</v>
+        <v>1645</v>
       </c>
       <c r="H12" t="n">
         <v>46.56</v>
@@ -1521,7 +1521,7 @@
         <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>252000</v>
+        <v>253000</v>
       </c>
       <c r="M12" t="n">
         <v>247500</v>
@@ -1530,7 +1530,7 @@
         <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>1226634938250</v>
+        <v>1314172114750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 업황 둔화 우려 속, 배당 및 최고점 돌파 기대.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 800건 토론 포착</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '배당']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13270</v>
+        <v>13290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'-0.08%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10808852235</v>
+        <v>10928957405</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5175</v>
+        <v>5210</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-0.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.39</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H14" t="n">
         <v>1.29</v>
@@ -1714,7 +1714,7 @@
         <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>55937056540</v>
+        <v>56316096570</v>
       </c>
       <c r="P14" t="n">
         <v>8980</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10520</v>
+        <v>10560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1.29</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
         <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H15" t="n">
         <v>19.22</v>
@@ -1806,7 +1806,7 @@
         <v>17.93</v>
       </c>
       <c r="O15" t="n">
-        <v>107952324185</v>
+        <v>109440415170</v>
       </c>
       <c r="P15" t="n">
         <v>22450</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8490</v>
+        <v>8510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F16" t="n">
         <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H16" t="n">
         <v>26.66</v>
@@ -1898,7 +1898,7 @@
         <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>9508386730</v>
+        <v>9719561855</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>부채 과다 및 재무 악화 우려, 개미 투자자 중심의 주가 흐름.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 111건 토론 포착</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['부채', '재무', '개미']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84450</v>
+        <v>84200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.03%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F17" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="H17" t="n">
         <v>23.37</v>
@@ -1990,7 +1990,7 @@
         <v>23.45</v>
       </c>
       <c r="O17" t="n">
-        <v>102220291550</v>
+        <v>105073996300</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대감 속 공매도 세력과의 갈등, 10만원 돌파 전망.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 220건 토론 포착</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '공매도']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18580</v>
+        <v>17110</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.88%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H18" t="n">
-        <v>10.64</v>
+        <v>0.45</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19130</v>
+        <v>17550</v>
       </c>
       <c r="K18" t="n">
-        <v>19160</v>
+        <v>17150</v>
       </c>
       <c r="L18" t="n">
-        <v>19340</v>
+        <v>18860</v>
       </c>
       <c r="M18" t="n">
-        <v>18330</v>
+        <v>16710</v>
       </c>
       <c r="N18" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>39190443930</v>
+        <v>154576656285</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R18" t="n">
-        <v>-204000</v>
+        <v>-60000</v>
       </c>
       <c r="S18" t="n">
-        <v>-37000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려 및 주가 10만원 이상 상승 기대, 대형 계약 임박.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 160건 토론 포착</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가조작']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31450</v>
+        <v>18650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.34</v>
+        <v>0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
-        <v>1093</v>
+        <v>320</v>
       </c>
       <c r="H19" t="n">
-        <v>17.16</v>
+        <v>10.64</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32450</v>
+        <v>19130</v>
       </c>
       <c r="K19" t="n">
-        <v>32850</v>
+        <v>19160</v>
       </c>
       <c r="L19" t="n">
-        <v>32850</v>
+        <v>19340</v>
       </c>
       <c r="M19" t="n">
-        <v>30900</v>
+        <v>18330</v>
       </c>
       <c r="N19" t="n">
-        <v>17.5</v>
+        <v>10.53</v>
       </c>
       <c r="O19" t="n">
-        <v>7632575875</v>
+        <v>40581000885</v>
       </c>
       <c r="P19" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-71000</v>
+        <v>-204000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 198건 토론 포착</t>
+          <t>[데이터 분석] '시장 주도주' 중심 96건 토론 포착</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16980</v>
+        <v>31450</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="G20" t="n">
-        <v>316</v>
+        <v>1100</v>
       </c>
       <c r="H20" t="n">
-        <v>0.45</v>
+        <v>17.16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17550</v>
+        <v>32450</v>
       </c>
       <c r="K20" t="n">
-        <v>17150</v>
+        <v>32850</v>
       </c>
       <c r="L20" t="n">
-        <v>18860</v>
+        <v>32850</v>
       </c>
       <c r="M20" t="n">
-        <v>16710</v>
+        <v>30900</v>
       </c>
       <c r="N20" t="n">
-        <v>0.35</v>
+        <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>154182102665</v>
+        <v>7878222225</v>
       </c>
       <c r="P20" t="n">
-        <v>30550</v>
+        <v>69200</v>
       </c>
       <c r="Q20" t="n">
-        <v>6100</v>
+        <v>24150</v>
       </c>
       <c r="R20" t="n">
-        <v>-60000</v>
+        <v>-71000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 160건 토론 포착</t>
+          <t>유럽 담관암 신약 신청 관련 불확실성 속 FDA 실패 가능성 제기. 과거 신약 실패 경험과 공모주 청약 시점의 유럽 신청에 대한 의구심이 공존.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['담관암', 'FDA', '신약 신청']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5910</v>
+        <v>14040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.28%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="G21" t="n">
-        <v>163</v>
+        <v>484</v>
       </c>
       <c r="H21" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K21" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L21" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M21" t="n">
-        <v>5630</v>
+        <v>13780</v>
       </c>
       <c r="N21" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>39920921595</v>
+        <v>29367177610</v>
       </c>
       <c r="P21" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q21" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R21" t="n">
-        <v>389000</v>
+        <v>-11000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>클래리티법 부결 속 가상자산 규제 입법 지연. 삼성 공급 계약 및 양자보안 샌즈랩 급등. 공매도 증가 및 대규모 장대음봉.</t>
+          <t>[데이터 분석] '시장 주도주' 중심 222건 토론 포착</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['클래리티법', '양자보안', '공매도']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13880</v>
+        <v>5910</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E22" t="n">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
-        <v>466</v>
+        <v>166</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K22" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L22" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M22" t="n">
-        <v>13780</v>
+        <v>5630</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O22" t="n">
-        <v>28535007025</v>
+        <v>40100667785</v>
       </c>
       <c r="P22" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q22" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R22" t="n">
-        <v>-11000</v>
+        <v>389000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 217건 토론 포착</t>
+          <t>클래리티법 부결 속 가상자산 규제 입법 지연. 삼성 공급 계약 및 양자보안 샌즈랩 급등. 공매도 증가 및 대규모 장대음봉.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['클래리티법', '양자보안', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>158430</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260916_12.xlsx
+++ b/data/trending_integrated_20260916_12.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F2" t="n">
         <v>143</v>
       </c>
       <c r="G2" t="n">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7383857730</v>
+        <v>7395358530</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오 인수 관련하여 합법 카지노 사업 확장 기대감이 높으나, 인수 조건 및 시총 관련 분석은 미흡. 공매도 숏스퀴즈 발생 가능성 언급.</t>
+          <t>카카오의 카지노 사업 인수를 통한 M&amp;A 기대감으로 급등. 공매도 숏스퀴즈 가능성 언급. 클래리티법 부결은 악재로 작용할 수 있음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오 인수', '카지노', '숏스퀴즈']</t>
+          <t>['카카오 인수', '카지노', '공매도 숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13610</v>
+        <v>13540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.20%</t>
+          <t>'+26.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>168301490000</v>
+        <v>169616414395</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 대장주로서의 기대감, 광통신, 방산 등 연관 섹터 동반 상승. 강력한 상승 움직임 관찰.</t>
+          <t>6G 통신 대장주로 언급되나, 실적이 없고 거래량이 적어 투자에 주의가 필요한 상황. 단기 물량 이동 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['6G', '광통신', '대장주']</t>
+          <t>['6G 통신', '실적 부재', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16320</v>
+        <v>16270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.42%</t>
+          <t>'+15.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="F4" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="G4" t="n">
-        <v>1308</v>
+        <v>1392</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>485534431040</v>
+        <v>501731145630</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 285건 토론 포착</t>
+          <t>14000원 지지선 확보 및 급등 가능성 언급. 대량 매집 확인. 2만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['대량매집', '지지선', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4535</v>
+        <v>4490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.07%</t>
+          <t>'+8.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>289696176098</v>
+        <v>293304341796</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>적자 지속 리스크 및 주가 하락, 악질 종목으로 평가.</t>
+          <t>차트 기반 지지선 언급 및 추가 상승 기대. 운전 기술 언급. 적자 지속 리스크.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['적자', '리스크', '주가']</t>
+          <t>['지지선', '거래량', '적자']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3730</v>
+        <v>3735</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.12%</t>
+          <t>'+6.26%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>15660865813</v>
+        <v>15767677335</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>재탕 뉴스에 기반한 상승 기대감과 달리, 상당한 규모의 적자 지속으로 인한 상폐 가능성 및 주가 하락 전망 제기. 투자자 주의 요구.</t>
+          <t>재무 상태 악화 및 적자 지속 가능성이 제기되며, 상폐 우려와 함께 주가 하락 가능성 농후. 기존 뉴스는 재탕 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '재탕 뉴스']</t>
+          <t>['적자 지속', '상폐 우려', '주가 하락']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7200</v>
+        <v>7190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+4.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>73745200210</v>
+        <v>73934305010</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3470</v>
+        <v>3495</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>95694375397</v>
+        <v>96636966476</v>
       </c>
       <c r="P8" t="n">
         <v>5100</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 82건 토론 포착</t>
+          <t>양자내성암호 및 양자암호 해독키 공급 이슈. 미국 광통신 보안주 상승 영향. 대한광통신과 유사.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['양자암호', '해독키', '보안주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192900</v>
+        <v>193500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+3.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>407500031750</v>
+        <v>418518524100</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1727000</v>
+        <v>10370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>480</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>1847</v>
+        <v>220</v>
       </c>
       <c r="H10" t="n">
-        <v>50.2</v>
+        <v>0.67</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1690000</v>
+        <v>10120</v>
       </c>
       <c r="K10" t="n">
-        <v>1686000</v>
+        <v>10190</v>
       </c>
       <c r="L10" t="n">
-        <v>1731000</v>
+        <v>10920</v>
       </c>
       <c r="M10" t="n">
-        <v>1686000</v>
+        <v>9790</v>
       </c>
       <c r="N10" t="n">
-        <v>50.27</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2187352077000</v>
+        <v>107144236320</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>15960</v>
       </c>
       <c r="Q10" t="n">
-        <v>331500</v>
+        <v>3500</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-9000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 800건 토론 포착</t>
+          <t>미프진 관련 재료 소멸 및 도입 공식화 기대 공존. 주가 변동성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['미프진', '재료소멸', '도입']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10310</v>
+        <v>1729500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.88%</t>
+          <t>'+2.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>471</v>
       </c>
       <c r="G11" t="n">
-        <v>228</v>
+        <v>1877</v>
       </c>
       <c r="H11" t="n">
-        <v>0.67</v>
+        <v>50.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10120</v>
+        <v>1690000</v>
       </c>
       <c r="K11" t="n">
-        <v>10190</v>
+        <v>1686000</v>
       </c>
       <c r="L11" t="n">
-        <v>10920</v>
+        <v>1733000</v>
       </c>
       <c r="M11" t="n">
-        <v>9790</v>
+        <v>1686000</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>50.27</v>
       </c>
       <c r="O11" t="n">
-        <v>105403113090</v>
+        <v>2319527717000</v>
       </c>
       <c r="P11" t="n">
-        <v>15960</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3500</v>
+        <v>331500</v>
       </c>
       <c r="R11" t="n">
-        <v>-9000</v>
+        <v>-12000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 108건 토론 포착</t>
+          <t>젠슨 황 언급 및 기관 매수 기대. 자사주 매입 및 소각 기대. 240만원 목표.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['자사주매입', '기관매수', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>252500</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+1.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G12" t="n">
-        <v>1645</v>
+        <v>1543</v>
       </c>
       <c r="H12" t="n">
         <v>46.56</v>
@@ -1521,7 +1521,7 @@
         <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>253000</v>
+        <v>253500</v>
       </c>
       <c r="M12" t="n">
         <v>247500</v>
@@ -1530,7 +1530,7 @@
         <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>1314172114750</v>
+        <v>1412963365250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 800건 토론 포착</t>
+          <t>3분기 실적 및 배당금 언급. 정치적 이슈와 함께 주가 하락 우려. 15만원 예상.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['실적', '배당금', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13290</v>
+        <v>13330</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.08%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10928957405</v>
+        <v>11126663395</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5210</v>
+        <v>5180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.38%</t>
+          <t>'-0.96%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.39</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H14" t="n">
         <v>1.29</v>
@@ -1714,7 +1714,7 @@
         <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>56316096570</v>
+        <v>59111918250</v>
       </c>
       <c r="P14" t="n">
         <v>8980</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10560</v>
+        <v>8520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-1.05%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.29</v>
+        <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>153</v>
+        <v>343</v>
       </c>
       <c r="H15" t="n">
-        <v>19.22</v>
+        <v>26.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10660</v>
+        <v>8610</v>
       </c>
       <c r="K15" t="n">
-        <v>10500</v>
+        <v>8600</v>
       </c>
       <c r="L15" t="n">
-        <v>10900</v>
+        <v>8610</v>
       </c>
       <c r="M15" t="n">
-        <v>10060</v>
+        <v>8430</v>
       </c>
       <c r="N15" t="n">
-        <v>17.93</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>109440415170</v>
+        <v>9918646140</v>
       </c>
       <c r="P15" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>1760</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-569000</v>
+        <v>-528000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>-36000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>거래량 증가에도 불구하고 주가 하락. 단기 급등 가능성 언급.</t>
+          <t>삼성디스플레이와 비교하며 PBR 저평가 언급. 외인 매도세 지속 및 재무 상태 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['거래량', '주가', '상승']</t>
+          <t>['PBR', '외인매도', '재무']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8510</v>
+        <v>10500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.5</v>
+        <v>1.29</v>
       </c>
       <c r="E16" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>342</v>
+        <v>160</v>
       </c>
       <c r="H16" t="n">
-        <v>26.66</v>
+        <v>19.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8610</v>
+        <v>10660</v>
       </c>
       <c r="K16" t="n">
-        <v>8600</v>
+        <v>10500</v>
       </c>
       <c r="L16" t="n">
-        <v>8610</v>
+        <v>10900</v>
       </c>
       <c r="M16" t="n">
-        <v>8430</v>
+        <v>10060</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>17.93</v>
       </c>
       <c r="O16" t="n">
-        <v>9719561855</v>
+        <v>110717199600</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>1760</v>
       </c>
       <c r="R16" t="n">
-        <v>-528000</v>
+        <v>-569000</v>
       </c>
       <c r="S16" t="n">
-        <v>-36000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 111건 토론 포착</t>
+          <t>급등 가능성 언급. 차트와 거래량 기반 추가 상승 전망. 대한광통신 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['거래량', '차트', '상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84200</v>
+        <v>84400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G17" t="n">
-        <v>686</v>
+        <v>727</v>
       </c>
       <c r="H17" t="n">
         <v>23.37</v>
@@ -1990,7 +1990,7 @@
         <v>23.45</v>
       </c>
       <c r="O17" t="n">
-        <v>105073996300</v>
+        <v>109455909850</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 220건 토론 포착</t>
+          <t>웨스팅하우스 지분 인수 기대감. 공매도 세력 언급 및 10만원 돌파 전망. 대미 투자 연기 이슈.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['웨스팅하우스', '지분인수', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17110</v>
+        <v>18705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="H18" t="n">
-        <v>0.45</v>
+        <v>10.64</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17550</v>
+        <v>19130</v>
       </c>
       <c r="K18" t="n">
-        <v>17150</v>
+        <v>19160</v>
       </c>
       <c r="L18" t="n">
-        <v>18860</v>
+        <v>19340</v>
       </c>
       <c r="M18" t="n">
-        <v>16710</v>
+        <v>18330</v>
       </c>
       <c r="N18" t="n">
-        <v>0.35</v>
+        <v>10.53</v>
       </c>
       <c r="O18" t="n">
-        <v>154576656285</v>
+        <v>41989174900</v>
       </c>
       <c r="P18" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-60000</v>
+        <v>-204000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 160건 토론 포착</t>
+          <t>대차해지 운동 동참 촉구. 주가 조작 및 공매도 세력 비판. 10만원 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['대차해지', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18650</v>
+        <v>17130</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H19" t="n">
-        <v>10.64</v>
+        <v>0.45</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19130</v>
+        <v>17550</v>
       </c>
       <c r="K19" t="n">
-        <v>19160</v>
+        <v>17150</v>
       </c>
       <c r="L19" t="n">
-        <v>19340</v>
+        <v>18860</v>
       </c>
       <c r="M19" t="n">
-        <v>18330</v>
+        <v>16710</v>
       </c>
       <c r="N19" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="O19" t="n">
-        <v>40581000885</v>
+        <v>155401533585</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R19" t="n">
-        <v>-204000</v>
+        <v>-60000</v>
       </c>
       <c r="S19" t="n">
-        <v>-37000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 96건 토론 포착</t>
+          <t>미국 보안주 강세와 연관되어 상승 기대감이 있으나, 개미 털기 및 인위적인 주가 하락 의혹 제기. 22,000원까지 상승 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['보안주', '개미 털기', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31450</v>
+        <v>31600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F20" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G20" t="n">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>7878222225</v>
+        <v>8107038225</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14040</v>
+        <v>5910</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.28%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E21" t="n">
-        <v>222</v>
+        <v>90</v>
       </c>
       <c r="F21" t="n">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>484</v>
+        <v>169</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K21" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L21" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M21" t="n">
-        <v>13780</v>
+        <v>5630</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O21" t="n">
-        <v>29367177610</v>
+        <v>40388258920</v>
       </c>
       <c r="P21" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q21" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R21" t="n">
-        <v>-11000</v>
+        <v>389000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>[데이터 분석] '시장 주도주' 중심 222건 토론 포착</t>
+          <t>클래리티법 부결 속 가상자산 규제 입법 지연. 삼성 공급 계약 및 양자보안 샌즈랩 급등. 공매도 증가 및 대규모 장대음봉.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['클래리티법', '양자보안', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5910</v>
+        <v>13870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-7.41%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="G22" t="n">
-        <v>166</v>
+        <v>494</v>
       </c>
       <c r="H22" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K22" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L22" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M22" t="n">
-        <v>5630</v>
+        <v>13520</v>
       </c>
       <c r="N22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>40100667785</v>
+        <v>30856524935</v>
       </c>
       <c r="P22" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q22" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R22" t="n">
-        <v>389000</v>
+        <v>-11000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>클래리티법 부결 속 가상자산 규제 입법 지연. 삼성 공급 계약 및 양자보안 샌즈랩 급등. 공매도 증가 및 대규모 장대음봉.</t>
+          <t>국제유가 상승 및 미국 오일 관련주 폭등으로 인한 기대감이 있으나, 비축유 방출 및 테마 종료 우려로 인한 급락 가능성 제기. 분봉상 하락 추세 확인.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['클래리티법', '양자보안', '공매도']</t>
+          <t>['국제유가', '오일 관련주', '비축유']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>024060</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260916_12.xlsx
+++ b/data/trending_integrated_20260916_12.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7395358530</v>
+        <v>7401971010</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 카지노 사업 인수를 통한 M&amp;A 기대감으로 급등. 공매도 숏스퀴즈 가능성 언급. 클래리티법 부결은 악재로 작용할 수 있음.</t>
+          <t>카카오의 잠재적 인수 및 합법 카지노 사업 확장 기대감에 따른 주가 상승 전망. 클래리티법 부결은 무관.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오 인수', '카지노', '공매도 숏스퀴즈']</t>
+          <t>['카카오 인수', '합법 카지노', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>169616414395</v>
+        <v>169987288925</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16270</v>
+        <v>16220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.06%</t>
+          <t>'+14.71%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F4" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G4" t="n">
-        <v>1392</v>
+        <v>1482</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>501731145630</v>
+        <v>511384083495</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>14000원 지지선 확보 및 급등 가능성 언급. 대량 매집 확인. 2만원 돌파 기대.</t>
+          <t>대규모 프로그램 매수세 유입 및 RFHIC, KMHW 등 관련주 강세에 따른 급등 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대량매집', '지지선', '급등']</t>
+          <t>['대량매집', '우상향', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4490</v>
+        <v>4485</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.98%</t>
+          <t>'+8.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F5" t="n">
         <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>293304341796</v>
+        <v>294892383215</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>차트 기반 지지선 언급 및 추가 상승 기대. 운전 기술 언급. 적자 지속 리스크.</t>
+          <t>미국 광통신 종목 상승에 따른 기대감 표출, 적자 지속 리스크 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['지지선', '거래량', '적자']</t>
+          <t>['광통신', '기대감', '적자']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
         <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>15767677335</v>
+        <v>15853463959</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7190</v>
+        <v>7210</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.20%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>73934305010</v>
+        <v>74144614125</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3495</v>
+        <v>3470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+3.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
         <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>96636966476</v>
+        <v>97030181929</v>
       </c>
       <c r="P8" t="n">
         <v>5100</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자내성암호 및 양자암호 해독키 공급 이슈. 미국 광통신 보안주 상승 영향. 대한광통신과 유사.</t>
+          <t>트럼프 행정명령 및 미국 보안주 상승에 따른 양자암호 관련주 주목. 매집 패턴 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자암호', '해독키', '보안주']</t>
+          <t>['양자암호', '보안주', '행정명령']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>193500</v>
+        <v>192900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.42%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H9" t="n">
         <v>75.66</v>
@@ -1254,7 +1254,7 @@
         <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>418518524100</v>
+        <v>423933805450</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10370</v>
+        <v>1725000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+2.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>473</v>
       </c>
       <c r="G10" t="n">
-        <v>220</v>
+        <v>1895</v>
       </c>
       <c r="H10" t="n">
-        <v>0.67</v>
+        <v>50.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10120</v>
+        <v>1690000</v>
       </c>
       <c r="K10" t="n">
-        <v>10190</v>
+        <v>1686000</v>
       </c>
       <c r="L10" t="n">
-        <v>10920</v>
+        <v>1733000</v>
       </c>
       <c r="M10" t="n">
-        <v>9790</v>
+        <v>1686000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>107144236320</v>
+        <v>2384624697500</v>
       </c>
       <c r="P10" t="n">
-        <v>15960</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3500</v>
+        <v>331500</v>
       </c>
       <c r="R10" t="n">
-        <v>-9000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미프진 관련 재료 소멸 및 도입 공식화 기대 공존. 주가 변동성 언급.</t>
+          <t>자사주 매입 및 소각 기대감, 반도체 실적 시즌 도래에 따른 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '도입']</t>
+          <t>['자사주', '반도체', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1729500</v>
+        <v>18670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.34%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>471</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>1877</v>
+        <v>347</v>
       </c>
       <c r="H11" t="n">
-        <v>50.2</v>
+        <v>10.64</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1690000</v>
+        <v>18340</v>
       </c>
       <c r="K11" t="n">
-        <v>1686000</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1733000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1686000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>50.27</v>
+        <v>10.53</v>
       </c>
       <c r="O11" t="n">
-        <v>2319527717000</v>
+        <v>42531000000</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>331500</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-12000</v>
+        <v>-204000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000</v>
+        <v>-37000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>젠슨 황 언급 및 기관 매수 기대. 자사주 매입 및 소각 기대. 240만원 목표.</t>
+          <t>대규모 계약 기대감 및 공매도 세력과의 수급 싸움 전망. 대차 해지 운동 독려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주매입', '기관매수', '반도체']</t>
+          <t>['대차해지', '공매도', '계약']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253000</v>
+        <v>10280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.81%</t>
+          <t>'+1.58%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>454</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>1543</v>
+        <v>227</v>
       </c>
       <c r="H12" t="n">
-        <v>46.56</v>
+        <v>0.67</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>248500</v>
+        <v>10120</v>
       </c>
       <c r="K12" t="n">
-        <v>248000</v>
+        <v>10190</v>
       </c>
       <c r="L12" t="n">
-        <v>253500</v>
+        <v>10920</v>
       </c>
       <c r="M12" t="n">
-        <v>247500</v>
+        <v>9790</v>
       </c>
       <c r="N12" t="n">
-        <v>46.57</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1412963365250</v>
+        <v>108337734550</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q12" t="n">
-        <v>76700</v>
+        <v>3500</v>
       </c>
       <c r="R12" t="n">
-        <v>-573000</v>
+        <v>-9000</v>
       </c>
       <c r="S12" t="n">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 및 배당금 언급. 정치적 이슈와 함께 주가 하락 우려. 15만원 예상.</t>
+          <t>미프진 공급 공식화 재료 반영 및 허가 발표 기대감에 따른 상승 가능성 분석.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '배당금', '정치']</t>
+          <t>['미프진', '공식화', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13330</v>
+        <v>252250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>454</v>
       </c>
       <c r="G13" t="n">
-        <v>254</v>
+        <v>1519</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,130 +1607,130 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13300</v>
+        <v>248500</v>
       </c>
       <c r="K13" t="n">
-        <v>13490</v>
+        <v>248000</v>
       </c>
       <c r="L13" t="n">
-        <v>13940</v>
+        <v>253500</v>
       </c>
       <c r="M13" t="n">
-        <v>13230</v>
+        <v>247500</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>46.57</v>
       </c>
       <c r="O13" t="n">
-        <v>11126663395</v>
+        <v>1462149483750</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>76700</v>
       </c>
       <c r="R13" t="n">
-        <v>-22000</v>
+        <v>-573000</v>
       </c>
       <c r="S13" t="n">
-        <v>3000</v>
+        <v>259000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>3분기 실적 호조 및 배당 기대감 속 정치적 이슈에 따른 주가 변동성 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['실적', '배당', '정치이슈']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5180</v>
+        <v>13420</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.96%</t>
+          <t>'+0.90%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.39</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="H14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5230</v>
+        <v>13300</v>
       </c>
       <c r="K14" t="n">
-        <v>5750</v>
+        <v>13490</v>
       </c>
       <c r="L14" t="n">
-        <v>5880</v>
+        <v>13940</v>
       </c>
       <c r="M14" t="n">
-        <v>5120</v>
+        <v>13230</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>59111918250</v>
+        <v>11762879135</v>
       </c>
       <c r="P14" t="n">
-        <v>8980</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>2795</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>308000</v>
+        <v>-22000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8520</v>
+        <v>8510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H15" t="n">
         <v>26.66</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>9918646140</v>
+        <v>10043989230</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1851,123 +1851,123 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10500</v>
+        <v>5160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.34%</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>74</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>155</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.29</v>
       </c>
-      <c r="E16" t="n">
-        <v>97</v>
-      </c>
-      <c r="F16" t="n">
-        <v>62</v>
-      </c>
-      <c r="G16" t="n">
-        <v>160</v>
-      </c>
-      <c r="H16" t="n">
-        <v>19.22</v>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10660</v>
+        <v>5230</v>
       </c>
       <c r="K16" t="n">
-        <v>10500</v>
+        <v>5750</v>
       </c>
       <c r="L16" t="n">
-        <v>10900</v>
+        <v>5880</v>
       </c>
       <c r="M16" t="n">
-        <v>10060</v>
+        <v>5120</v>
       </c>
       <c r="N16" t="n">
-        <v>17.93</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>110717199600</v>
+        <v>59661114090</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>8980</v>
       </c>
       <c r="Q16" t="n">
-        <v>1760</v>
+        <v>2795</v>
       </c>
       <c r="R16" t="n">
-        <v>-569000</v>
+        <v>308000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>급등 가능성 언급. 차트와 거래량 기반 추가 상승 전망. 대한광통신 동반 상승 기대.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['거래량', '차트', '상승']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84400</v>
+        <v>10480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>1.29</v>
       </c>
       <c r="E17" t="n">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>727</v>
+        <v>165</v>
       </c>
       <c r="H17" t="n">
-        <v>23.37</v>
+        <v>19.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>86200</v>
+        <v>10660</v>
       </c>
       <c r="K17" t="n">
-        <v>86200</v>
+        <v>10500</v>
       </c>
       <c r="L17" t="n">
-        <v>86300</v>
+        <v>10900</v>
       </c>
       <c r="M17" t="n">
-        <v>83500</v>
+        <v>10060</v>
       </c>
       <c r="N17" t="n">
-        <v>23.45</v>
+        <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>109455909850</v>
+        <v>111424610205</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>1760</v>
       </c>
       <c r="R17" t="n">
-        <v>-137000</v>
+        <v>-569000</v>
       </c>
       <c r="S17" t="n">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대감. 공매도 세력 언급 및 10만원 돌파 전망. 대미 투자 연기 이슈.</t>
+          <t>주가 상승 기대감 속 투자 주의 해제 여부에 따른 단기 변동성 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '공매도']</t>
+          <t>['투자주의', '거래량', '차트']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18705</v>
+        <v>84200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.22%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>234</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
-        <v>339</v>
+        <v>733</v>
       </c>
       <c r="H18" t="n">
-        <v>10.64</v>
+        <v>23.37</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19130</v>
+        <v>86200</v>
       </c>
       <c r="K18" t="n">
-        <v>19160</v>
+        <v>86200</v>
       </c>
       <c r="L18" t="n">
-        <v>19340</v>
+        <v>86300</v>
       </c>
       <c r="M18" t="n">
-        <v>18330</v>
+        <v>83500</v>
       </c>
       <c r="N18" t="n">
-        <v>10.53</v>
+        <v>23.45</v>
       </c>
       <c r="O18" t="n">
-        <v>41989174900</v>
+        <v>111717891800</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-204000</v>
+        <v>-137000</v>
       </c>
       <c r="S18" t="n">
-        <v>-37000</v>
+        <v>-5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 촉구. 주가 조작 및 공매도 세력 비판. 10만원 이상 상승 기대.</t>
+          <t>웨스팅하우스 지분 인수 관련 기대감 속 공매도 공방 및 단기 변동성 예상.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가조작']</t>
+          <t>['웨스팅하우스', '공매도', '지분인수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17130</v>
+        <v>17100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F19" t="n">
         <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H19" t="n">
         <v>0.45</v>
@@ -2174,7 +2174,7 @@
         <v>0.35</v>
       </c>
       <c r="O19" t="n">
-        <v>155401533585</v>
+        <v>155738713710</v>
       </c>
       <c r="P19" t="n">
         <v>30550</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 연관되어 상승 기대감이 있으나, 개미 털기 및 인위적인 주가 하락 의혹 제기. 22,000원까지 상승 전망.</t>
+          <t>미국 보안주 강세 속 상용화 및 매출 발생 기대감. 개미 털기 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['보안주', '개미 털기', '주가 하락']</t>
+          <t>['보안주', '상용화', '개미털기']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F20" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G20" t="n">
-        <v>1104</v>
+        <v>1080</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>8107038225</v>
+        <v>8201152375</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5910</v>
+        <v>5890</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.66%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-2.04</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H21" t="n">
         <v>0.98</v>
@@ -2358,7 +2358,7 @@
         <v>3.02</v>
       </c>
       <c r="O21" t="n">
-        <v>40388258920</v>
+        <v>40497539040</v>
       </c>
       <c r="P21" t="n">
         <v>11370</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13870</v>
+        <v>13980</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.41%</t>
+          <t>'-6.68%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>220</v>
       </c>
       <c r="F22" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G22" t="n">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>30856524935</v>
+        <v>31300384665</v>
       </c>
       <c r="P22" t="n">
         <v>36200</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 미국 오일 관련주 폭등으로 인한 기대감이 있으나, 비축유 방출 및 테마 종료 우려로 인한 급락 가능성 제기. 분봉상 하락 추세 확인.</t>
+          <t>국제유가 상승 전망에도 불구하고 비축유 및 역배열 분봉으로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['국제유가', '오일 관련주', '비축유']</t>
+          <t>['국제유가', '비축유', '역배열']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20260916_12.xlsx
+++ b/data/trending_integrated_20260916_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G2" t="n">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7401971010</v>
+        <v>7406498370</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13540</v>
+        <v>13590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.54%</t>
+          <t>'+27.01%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>169987288925</v>
+        <v>170355646375</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 대장주로 언급되나, 실적이 없고 거래량이 적어 투자에 주의가 필요한 상황. 단기 물량 이동 가능성.</t>
+          <t>6G 통신 대장주로서의 기대감 형성. 빛과전자 등 관련주 동반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['6G 통신', '실적 부재', '거래량']</t>
+          <t>['6G 통신', '대장주', '관련주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16220</v>
+        <v>16120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.71%</t>
+          <t>'+14.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F4" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G4" t="n">
-        <v>1482</v>
+        <v>1519</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>511384083495</v>
+        <v>519536619680</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대규모 프로그램 매수세 유입 및 RFHIC, KMHW 등 관련주 강세에 따른 급등 전망.</t>
+          <t>외국인/기관 600억 대량 순매수 확인. 미국 자회사 대규모 광통신 수주 및 10만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대량매집', '우상향', '대장주']</t>
+          <t>['대량 순매수', '광통신 수주', '외국인/기관']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4485</v>
+        <v>4460</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.86%</t>
+          <t>'+8.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>294892383215</v>
+        <v>296344023965</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신 종목 상승에 따른 기대감 표출, 적자 지속 리스크 존재.</t>
+          <t>광통신 관련주 동반 상승 기대감 속에서 급등 시도. 4천원 지지선 확보 및 거래량 동반 상승 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '기대감', '적자']</t>
+          <t>['광통신', '거래량', '지지선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3735</v>
+        <v>3760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.26%</t>
+          <t>'+6.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
         <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -978,7 +978,7 @@
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>15853463959</v>
+        <v>16183614574</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>재무 상태 악화 및 적자 지속 가능성이 제기되며, 상폐 우려와 함께 주가 하락 가능성 농후. 기존 뉴스는 재탕 가능성 언급.</t>
+          <t xml:space="preserve">최대주주 유한양행 보유에도 불구하고 주가 급락. 재탕 뉴스 및 25-26년 대규모 적자 전망으로 인한 투자 심리 위축.   </t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자 지속', '상폐 우려', '주가 하락']</t>
+          <t>['유한양행', '적자', '재탕 뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7210</v>
+        <v>7170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+3.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>74144614125</v>
+        <v>74305666905</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3470</v>
+        <v>192700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>75.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3360</v>
+        <v>187100</v>
       </c>
       <c r="K8" t="n">
-        <v>3570</v>
+        <v>187200</v>
       </c>
       <c r="L8" t="n">
-        <v>3910</v>
+        <v>195900</v>
       </c>
       <c r="M8" t="n">
-        <v>3345</v>
+        <v>186100</v>
       </c>
       <c r="N8" t="n">
-        <v>1.34</v>
+        <v>75.67</v>
       </c>
       <c r="O8" t="n">
-        <v>97030181929</v>
+        <v>432245585200</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>966</v>
+        <v>61800</v>
       </c>
       <c r="R8" t="n">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>트럼프 행정명령 및 미국 보안주 상승에 따른 양자암호 관련주 주목. 매집 패턴 관찰.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '행정명령']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192900</v>
+        <v>3455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-1.34</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c r="H9" t="n">
-        <v>75.66</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>187100</v>
+        <v>3360</v>
       </c>
       <c r="K9" t="n">
-        <v>187200</v>
+        <v>3570</v>
       </c>
       <c r="L9" t="n">
-        <v>195900</v>
+        <v>3910</v>
       </c>
       <c r="M9" t="n">
-        <v>186100</v>
+        <v>3345</v>
       </c>
       <c r="N9" t="n">
-        <v>75.67</v>
+        <v>1.34</v>
       </c>
       <c r="O9" t="n">
-        <v>423933805450</v>
+        <v>97363532056</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>5100</v>
       </c>
       <c r="Q9" t="n">
-        <v>61800</v>
+        <v>966</v>
       </c>
       <c r="R9" t="n">
-        <v>21000</v>
+        <v>9000</v>
       </c>
       <c r="S9" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>트럼프 행정명령 및 미국 보안주 상승에 따른 양자암호 관련주 주목. 매집 패턴 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['양자암호', '보안주', '행정명령']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1725000</v>
+        <v>1729000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+2.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G10" t="n">
-        <v>1895</v>
+        <v>1862</v>
       </c>
       <c r="H10" t="n">
         <v>50.2</v>
@@ -1346,7 +1346,7 @@
         <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>2384624697500</v>
+        <v>2445610852500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감, 반도체 실적 시즌 도래에 따른 상승 전망.</t>
+          <t>젠슨황 언급 및 자사주 매입/소각 기대감. 240만원 목표가 설정 및 반도체 실적 발표 시즌 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주', '반도체', '실적']</t>
+          <t>['자사주 매입', '반도체', '젠슨황']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18670</v>
+        <v>252750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+1.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>455</v>
       </c>
       <c r="G11" t="n">
-        <v>347</v>
+        <v>1471</v>
       </c>
       <c r="H11" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18340</v>
+        <v>248500</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>248000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>253500</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>247500</v>
       </c>
       <c r="N11" t="n">
-        <v>10.53</v>
+        <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>42531000000</v>
+        <v>1507060589250</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>-204000</v>
+        <v>-573000</v>
       </c>
       <c r="S11" t="n">
-        <v>-37000</v>
+        <v>259000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대규모 계약 기대감 및 공매도 세력과의 수급 싸움 전망. 대차 해지 운동 독려.</t>
+          <t>3분기 배당금 및 연말 최고점 돌파 기대감. 정치적 이슈와 함께 주가 부양 정책 관련 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '계약']</t>
+          <t>['배당금', '주가 부양', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="H12" t="n">
         <v>0.67</v>
@@ -1530,7 +1530,7 @@
         <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>108337734550</v>
+        <v>109754282070</v>
       </c>
       <c r="P12" t="n">
         <v>15960</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미프진 공급 공식화 재료 반영 및 허가 발표 기대감에 따른 상승 가능성 분석.</t>
+          <t>미프진 독점 공급 계약 체결에 따른 기대감 형성. 정부 허가 발표 임박 및 도입 시기 관련 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미프진', '공식화', '기대감']</t>
+          <t>['미프진', '독점 공급', '정부 허가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252250</v>
+        <v>13450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>454</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>1519</v>
+        <v>256</v>
       </c>
       <c r="H13" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>248500</v>
+        <v>13300</v>
       </c>
       <c r="K13" t="n">
-        <v>248000</v>
+        <v>13490</v>
       </c>
       <c r="L13" t="n">
-        <v>253500</v>
+        <v>13940</v>
       </c>
       <c r="M13" t="n">
-        <v>247500</v>
+        <v>13230</v>
       </c>
       <c r="N13" t="n">
-        <v>46.57</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1462149483750</v>
+        <v>12024670545</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>76700</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-573000</v>
+        <v>-22000</v>
       </c>
       <c r="S13" t="n">
-        <v>259000</v>
+        <v>3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 실적 호조 및 배당 기대감 속 정치적 이슈에 따른 주가 변동성 우려.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '배당', '정치이슈']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13420</v>
+        <v>8510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13300</v>
+        <v>8610</v>
       </c>
       <c r="K14" t="n">
-        <v>13490</v>
+        <v>8600</v>
       </c>
       <c r="L14" t="n">
-        <v>13940</v>
+        <v>8610</v>
       </c>
       <c r="M14" t="n">
-        <v>13230</v>
+        <v>8430</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O14" t="n">
-        <v>11762879135</v>
+        <v>10270338980</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-22000</v>
+        <v>-528000</v>
       </c>
       <c r="S14" t="n">
-        <v>3000</v>
+        <v>-36000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>삼성디스플레이 대비 낮은 가치 평가 및 부채 부담 언급. 외인 매도세 지속 및 실적 관련 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['PBR', '부채', '외인 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8510</v>
+        <v>20300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-1.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.5</v>
+        <v>-0.39</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
-        <v>346</v>
+        <v>246</v>
       </c>
       <c r="H15" t="n">
-        <v>26.66</v>
+        <v>28.51</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8610</v>
+        <v>20700</v>
       </c>
       <c r="K15" t="n">
-        <v>8600</v>
+        <v>20750</v>
       </c>
       <c r="L15" t="n">
-        <v>8610</v>
+        <v>20750</v>
       </c>
       <c r="M15" t="n">
-        <v>8430</v>
+        <v>20250</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>28.9</v>
       </c>
       <c r="O15" t="n">
-        <v>10043989230</v>
+        <v>21610763100</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>18440</v>
       </c>
       <c r="R15" t="n">
-        <v>-528000</v>
+        <v>-332000</v>
       </c>
       <c r="S15" t="n">
-        <v>-36000</v>
+        <v>-18000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성디스플레이와 비교하며 PBR 저평가 언급. 외인 매도세 지속 및 재무 상태 우려.</t>
+          <t>IBK투자증권 신규 매수 의견 및 목표주가 3만7000원 제시. 1.6조 LNG선 수주 등 긍정적 수주 실적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['PBR', '외인매도', '재무']</t>
+          <t>['수주', '목표주가', 'LNG선']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,222 +1844,222 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5160</v>
+        <v>10440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.34%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.39</v>
+        <v>1.29</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H16" t="n">
-        <v>1.29</v>
+        <v>19.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5230</v>
+        <v>10660</v>
       </c>
       <c r="K16" t="n">
-        <v>5750</v>
+        <v>10500</v>
       </c>
       <c r="L16" t="n">
-        <v>5880</v>
+        <v>10900</v>
       </c>
       <c r="M16" t="n">
-        <v>5120</v>
+        <v>10060</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>17.93</v>
       </c>
       <c r="O16" t="n">
-        <v>59661114090</v>
+        <v>112042854275</v>
       </c>
       <c r="P16" t="n">
-        <v>8980</v>
+        <v>22450</v>
       </c>
       <c r="Q16" t="n">
-        <v>2795</v>
+        <v>1760</v>
       </c>
       <c r="R16" t="n">
-        <v>308000</v>
+        <v>-569000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>투자주의 해제 예정 속에서 단기 급등 기대감 형성. 차트 분석 기반 거래량 동반 시 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['투자주의', '거래량', '차트']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10480</v>
+        <v>5120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>47</v>
+      </c>
+      <c r="G17" t="n">
+        <v>159</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.29</v>
       </c>
-      <c r="E17" t="n">
-        <v>99</v>
-      </c>
-      <c r="F17" t="n">
-        <v>63</v>
-      </c>
-      <c r="G17" t="n">
-        <v>165</v>
-      </c>
-      <c r="H17" t="n">
-        <v>19.22</v>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10660</v>
+        <v>5230</v>
       </c>
       <c r="K17" t="n">
-        <v>10500</v>
+        <v>5750</v>
       </c>
       <c r="L17" t="n">
-        <v>10900</v>
+        <v>5880</v>
       </c>
       <c r="M17" t="n">
-        <v>10060</v>
+        <v>5120</v>
       </c>
       <c r="N17" t="n">
-        <v>17.93</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
-        <v>111424610205</v>
+        <v>59965905340</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>8980</v>
       </c>
       <c r="Q17" t="n">
-        <v>1760</v>
+        <v>2795</v>
       </c>
       <c r="R17" t="n">
-        <v>-569000</v>
+        <v>308000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승 기대감 속 투자 주의 해제 여부에 따른 단기 변동성 전망.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['투자주의', '거래량', '차트']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84200</v>
+        <v>18720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>234</v>
+        <v>101</v>
       </c>
       <c r="F18" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>733</v>
+        <v>363</v>
       </c>
       <c r="H18" t="n">
-        <v>23.37</v>
+        <v>10.64</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>86200</v>
+        <v>19130</v>
       </c>
       <c r="K18" t="n">
-        <v>86200</v>
+        <v>19160</v>
       </c>
       <c r="L18" t="n">
-        <v>86300</v>
+        <v>19340</v>
       </c>
       <c r="M18" t="n">
-        <v>83500</v>
+        <v>18330</v>
       </c>
       <c r="N18" t="n">
-        <v>23.45</v>
+        <v>10.53</v>
       </c>
       <c r="O18" t="n">
-        <v>111717891800</v>
+        <v>43343941735</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-137000</v>
+        <v>-204000</v>
       </c>
       <c r="S18" t="n">
-        <v>-5000</v>
+        <v>-37000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 기대감 속 공매도 공방 및 단기 변동성 예상.</t>
+          <t>주가 조작 의혹 제기 및 대차 해지 운동 촉구. 대형 계약 임박 및 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '공매도', '지분인수']</t>
+          <t>['주가 조작', '대차 해지', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17100</v>
+        <v>84100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.56%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="G19" t="n">
-        <v>325</v>
+        <v>738</v>
       </c>
       <c r="H19" t="n">
-        <v>0.45</v>
+        <v>23.37</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17550</v>
+        <v>86200</v>
       </c>
       <c r="K19" t="n">
-        <v>17150</v>
+        <v>86200</v>
       </c>
       <c r="L19" t="n">
-        <v>18860</v>
+        <v>86300</v>
       </c>
       <c r="M19" t="n">
-        <v>16710</v>
+        <v>83500</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>23.45</v>
       </c>
       <c r="O19" t="n">
-        <v>155738713710</v>
+        <v>114414964050</v>
       </c>
       <c r="P19" t="n">
-        <v>30550</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>6100</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-60000</v>
+        <v>-137000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 속 상용화 및 매출 발생 기대감. 개미 털기 의혹 제기.</t>
+          <t>웨스팅하우스 지분 인수 관련 기대감 속 공매도 공방 및 단기 변동성 예상.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['보안주', '상용화', '개미털기']</t>
+          <t>['웨스팅하우스', '공매도', '지분인수']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31600</v>
+        <v>31650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-2.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.34</v>
       </c>
       <c r="E20" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F20" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G20" t="n">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="H20" t="n">
         <v>17.16</v>
@@ -2266,7 +2266,7 @@
         <v>17.5</v>
       </c>
       <c r="O20" t="n">
-        <v>8201152375</v>
+        <v>8302619275</v>
       </c>
       <c r="P20" t="n">
         <v>69200</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5890</v>
+        <v>17050</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.66%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.04</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="F21" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="G21" t="n">
-        <v>171</v>
+        <v>325</v>
       </c>
       <c r="H21" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6310</v>
+        <v>17550</v>
       </c>
       <c r="K21" t="n">
-        <v>6390</v>
+        <v>17150</v>
       </c>
       <c r="L21" t="n">
-        <v>6450</v>
+        <v>18860</v>
       </c>
       <c r="M21" t="n">
-        <v>5630</v>
+        <v>16710</v>
       </c>
       <c r="N21" t="n">
-        <v>3.02</v>
+        <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>40497539040</v>
+        <v>156127194740</v>
       </c>
       <c r="P21" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q21" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R21" t="n">
-        <v>389000</v>
+        <v>-60000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>클래리티법 부결 속 가상자산 규제 입법 지연. 삼성 공급 계약 및 양자보안 샌즈랩 급등. 공매도 증가 및 대규모 장대음봉.</t>
+          <t>미국 보안주 강세 속 상용화 및 매출 발생 기대감. 개미 털기 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['클래리티법', '양자보안', '공매도']</t>
+          <t>['보안주', '상용화', '개미털기']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13980</v>
+        <v>5900</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.68%</t>
+          <t>'-6.50%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E22" t="n">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="F22" t="n">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>503</v>
+        <v>172</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,58 +2435,150 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K22" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L22" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M22" t="n">
-        <v>13520</v>
+        <v>5630</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O22" t="n">
-        <v>31300384665</v>
+        <v>40665070720</v>
       </c>
       <c r="P22" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q22" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R22" t="n">
-        <v>-11000</v>
+        <v>389000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>국제유가 상승 전망에도 불구하고 비축유 및 역배열 분봉으로 인한 하락 우려.</t>
+          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['국제유가', '비축유', '역배열']</t>
+          <t>['클래리티법', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>158430</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-6.54%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>225</v>
+      </c>
+      <c r="F23" t="n">
+        <v>117</v>
+      </c>
+      <c r="G23" t="n">
+        <v>502</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>14980</v>
+      </c>
+      <c r="K23" t="n">
+        <v>15300</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15580</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13520</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>31755314665</v>
+      </c>
+      <c r="P23" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">국제 유가 상승 및 지정학적 리스크에도 불구하고 흥구석유 주가 하락. 에너지주 전반의 약세 및 비축유 방출 우려.  </t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['국제유가', '에너지주', '비축유']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
         <v>6</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>024060</t>
         </is>

--- a/data/trending_integrated_20260916_12.xlsx
+++ b/data/trending_integrated_20260916_12.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G2" t="n">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7406498370</v>
+        <v>7410649410</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13590</v>
+        <v>13630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.01%</t>
+          <t>'+27.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>170355646375</v>
+        <v>171332647690</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 대장주로서의 기대감 형성. 빛과전자 등 관련주 동반 상승 가능성 언급.</t>
+          <t>역대급 거래량 발생 속 급등. 6G 통신 대장주 언급. 실적 부진 지적.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['6G 통신', '대장주', '관련주']</t>
+          <t>['거래량', '6G']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16120</v>
+        <v>16050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.00%</t>
+          <t>'+13.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="F4" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G4" t="n">
-        <v>1519</v>
+        <v>1552</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>519536619680</v>
+        <v>535529370570</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인/기관 600억 대량 순매수 확인. 미국 자회사 대규모 광통신 수주 및 10만원 목표가 제시.</t>
+          <t>외국인/기관 대량 순매수 및 미국 자회사 수주 발표에 따른 급등 기대. 10만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대량 순매수', '광통신 수주', '외국인/기관']</t>
+          <t>['수주', '외국인']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4460</v>
+        <v>4420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.25%</t>
+          <t>'+7.28%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>296344023965</v>
+        <v>299282232307</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 관련주 동반 상승 기대감 속에서 급등 시도. 4천원 지지선 확보 및 거래량 동반 상승 가능성.</t>
+          <t>긍정적인 추세 및 상승 기대감 언급. 적자 지속 리스크 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '거래량', '지지선']</t>
+          <t>['상승', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3760</v>
+        <v>3680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.97%</t>
+          <t>'+4.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="H6" t="n">
         <v>3.11</v>
@@ -972,13 +972,13 @@
         <v>4140</v>
       </c>
       <c r="M6" t="n">
-        <v>3685</v>
+        <v>3665</v>
       </c>
       <c r="N6" t="n">
         <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>16183614574</v>
+        <v>16537759538</v>
       </c>
       <c r="P6" t="n">
         <v>16110</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t xml:space="preserve">최대주주 유한양행 보유에도 불구하고 주가 급락. 재탕 뉴스 및 25-26년 대규모 적자 전망으로 인한 투자 심리 위축.   </t>
+          <t>최대주주 유한양행 언급에도 불구하고, 투자자들의 불신과 대규모 적자 및 상폐 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유한양행', '적자', '재탕 뉴스']</t>
+          <t>['적자', '상폐', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7170</v>
+        <v>7160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
         <v>0.79</v>
@@ -1070,7 +1070,7 @@
         <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>74305666905</v>
+        <v>75169632055</v>
       </c>
       <c r="P7" t="n">
         <v>10360</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>192700</v>
+        <v>193400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H8" t="n">
         <v>75.66</v>
@@ -1162,7 +1162,7 @@
         <v>75.67</v>
       </c>
       <c r="O8" t="n">
-        <v>432245585200</v>
+        <v>441158150050</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3455</v>
+        <v>3465</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+3.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-1.34</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>1.34</v>
       </c>
       <c r="O9" t="n">
-        <v>97363532056</v>
+        <v>98183650728</v>
       </c>
       <c r="P9" t="n">
         <v>5100</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>트럼프 행정명령 및 미국 보안주 상승에 따른 양자암호 관련주 주목. 매집 패턴 관찰.</t>
+          <t>양자내성암호 이슈와 연계된 급등 기대. 글로벌 기업 독점 공급 언급. 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '행정명령']</t>
+          <t>['양자내성암호', '독점공급']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1729000</v>
+        <v>1734000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.31%</t>
+          <t>'+2.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G10" t="n">
-        <v>1862</v>
+        <v>1848</v>
       </c>
       <c r="H10" t="n">
         <v>50.2</v>
@@ -1337,7 +1337,7 @@
         <v>1686000</v>
       </c>
       <c r="L10" t="n">
-        <v>1733000</v>
+        <v>1735000</v>
       </c>
       <c r="M10" t="n">
         <v>1686000</v>
@@ -1346,7 +1346,7 @@
         <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>2445610852500</v>
+        <v>2551071405500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>젠슨황 언급 및 자사주 매입/소각 기대감. 240만원 목표가 설정 및 반도체 실적 발표 시즌 관련 언급.</t>
+          <t>젠슨황 관련 기대감 및 자사주 매입/소각 통한 주가 상승 전망. 금리 인상 영향 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['자사주 매입', '반도체', '젠슨황']</t>
+          <t>['자사주매입', '젠슨황']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252750</v>
+        <v>13545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.71%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>455</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>1471</v>
+        <v>261</v>
       </c>
       <c r="H11" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248500</v>
+        <v>13300</v>
       </c>
       <c r="K11" t="n">
-        <v>248000</v>
+        <v>13490</v>
       </c>
       <c r="L11" t="n">
-        <v>253500</v>
+        <v>13940</v>
       </c>
       <c r="M11" t="n">
-        <v>247500</v>
+        <v>13230</v>
       </c>
       <c r="N11" t="n">
-        <v>46.57</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1507060589250</v>
+        <v>12932865250</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q11" t="n">
-        <v>76700</v>
+        <v>3200</v>
       </c>
       <c r="R11" t="n">
-        <v>-573000</v>
+        <v>-22000</v>
       </c>
       <c r="S11" t="n">
-        <v>259000</v>
+        <v>3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 배당금 및 연말 최고점 돌파 기대감. 정치적 이슈와 함께 주가 부양 정책 관련 논의.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당금', '주가 부양', '반도체']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10280</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.58%</t>
+          <t>'+1.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>454</v>
       </c>
       <c r="G12" t="n">
-        <v>248</v>
+        <v>1458</v>
       </c>
       <c r="H12" t="n">
-        <v>0.67</v>
+        <v>46.56</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10120</v>
+        <v>248500</v>
       </c>
       <c r="K12" t="n">
-        <v>10190</v>
+        <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>10920</v>
+        <v>253500</v>
       </c>
       <c r="M12" t="n">
-        <v>9790</v>
+        <v>247500</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>109754282070</v>
+        <v>1576595460500</v>
       </c>
       <c r="P12" t="n">
-        <v>15960</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3500</v>
+        <v>76700</v>
       </c>
       <c r="R12" t="n">
-        <v>-9000</v>
+        <v>-573000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미프진 독점 공급 계약 체결에 따른 기대감 형성. 정부 허가 발표 임박 및 도입 시기 관련 논의.</t>
+          <t>총선, 정치적 이슈에 따른 주가 하락 우려. 배당 및 실적 기대감 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미프진', '독점 공급', '정부 허가']</t>
+          <t>['배당금', '이재명']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,99 +1568,99 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13450</v>
+        <v>10160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>253</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>10120</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10190</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10920</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9790</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>111702467940</v>
+      </c>
+      <c r="P13" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>52</v>
-      </c>
-      <c r="F13" t="n">
-        <v>43</v>
-      </c>
-      <c r="G13" t="n">
-        <v>256</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>13300</v>
-      </c>
-      <c r="K13" t="n">
-        <v>13490</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13940</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13230</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>12024670545</v>
-      </c>
-      <c r="P13" t="n">
-        <v>19380</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3200</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-22000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3000</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
+          <t>미프진 독점 공급 재료로 인한 단기 주가 상승 기대. 도입 시점 불확실성 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가', '호재', '투자심리']</t>
+          <t>['미프진', '독점공급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="H14" t="n">
         <v>26.66</v>
@@ -1714,7 +1714,7 @@
         <v>27.16</v>
       </c>
       <c r="O14" t="n">
-        <v>10270338980</v>
+        <v>10482288950</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성디스플레이 대비 낮은 가치 평가 및 부채 부담 언급. 외인 매도세 지속 및 실적 관련 부정적 전망.</t>
+          <t>삼성디스플레이와 비교되며 저평가 논란. 경영진 성과급 및 부채 문제 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['PBR', '부채', '외인 매도']</t>
+          <t>['PBR', '삼성디스플레이']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20300</v>
+        <v>18830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.93%</t>
+          <t>'-1.57%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.39</v>
+        <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>246</v>
+        <v>367</v>
       </c>
       <c r="H15" t="n">
-        <v>28.51</v>
+        <v>10.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>20700</v>
+        <v>19130</v>
       </c>
       <c r="K15" t="n">
-        <v>20750</v>
+        <v>19160</v>
       </c>
       <c r="L15" t="n">
-        <v>20750</v>
+        <v>19340</v>
       </c>
       <c r="M15" t="n">
-        <v>20250</v>
+        <v>18330</v>
       </c>
       <c r="N15" t="n">
-        <v>28.9</v>
+        <v>10.53</v>
       </c>
       <c r="O15" t="n">
-        <v>21610763100</v>
+        <v>44902245845</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>18440</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-332000</v>
+        <v>-204000</v>
       </c>
       <c r="S15" t="n">
-        <v>-18000</v>
+        <v>-37000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>IBK투자증권 신규 매수 의견 및 목표주가 3만7000원 제시. 1.6조 LNG선 수주 등 긍정적 수주 실적.</t>
+          <t>주가 조작 의혹 제기 및 대차 해지 운동 촉구. 대형 계약 임박 및 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '목표주가', 'LNG선']</t>
+          <t>['주가 조작', '대차 해지', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10440</v>
+        <v>20300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-1.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.29</v>
+        <v>-0.39</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G16" t="n">
-        <v>167</v>
+        <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>19.22</v>
+        <v>28.51</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>10660</v>
+        <v>20700</v>
       </c>
       <c r="K16" t="n">
-        <v>10500</v>
+        <v>20750</v>
       </c>
       <c r="L16" t="n">
-        <v>10900</v>
+        <v>20750</v>
       </c>
       <c r="M16" t="n">
-        <v>10060</v>
+        <v>20250</v>
       </c>
       <c r="N16" t="n">
-        <v>17.93</v>
+        <v>28.9</v>
       </c>
       <c r="O16" t="n">
-        <v>112042854275</v>
+        <v>22052630425</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>1760</v>
+        <v>18440</v>
       </c>
       <c r="R16" t="n">
-        <v>-569000</v>
+        <v>-332000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-18000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>투자주의 해제 예정 속에서 단기 급등 기대감 형성. 차트 분석 기반 거래량 동반 시 상승 전망.</t>
+          <t>IBK투자증권 목표주가 상향에도 불구하고 주가 상승 부진. 수주 대비 주가 미반영 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투자주의', '거래량', '차트']</t>
+          <t>['수주', '목표주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5120</v>
+        <v>10430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.39</v>
+        <v>1.29</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H17" t="n">
-        <v>1.29</v>
+        <v>19.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5230</v>
+        <v>10660</v>
       </c>
       <c r="K17" t="n">
-        <v>5750</v>
+        <v>10500</v>
       </c>
       <c r="L17" t="n">
-        <v>5880</v>
+        <v>10900</v>
       </c>
       <c r="M17" t="n">
-        <v>5120</v>
+        <v>10060</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>17.93</v>
       </c>
       <c r="O17" t="n">
-        <v>59965905340</v>
+        <v>113622000820</v>
       </c>
       <c r="P17" t="n">
-        <v>8980</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>2795</v>
+        <v>1760</v>
       </c>
       <c r="R17" t="n">
-        <v>308000</v>
+        <v>-569000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
+          <t>300만주 흡수 후 급등 가능성 언급. 기타법인 매도 및 투자주의 해제 예정.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '계약']</t>
+          <t>['거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18720</v>
+        <v>84100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="G18" t="n">
-        <v>363</v>
+        <v>769</v>
       </c>
       <c r="H18" t="n">
-        <v>10.64</v>
+        <v>23.37</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19130</v>
+        <v>86200</v>
       </c>
       <c r="K18" t="n">
-        <v>19160</v>
+        <v>86200</v>
       </c>
       <c r="L18" t="n">
-        <v>19340</v>
+        <v>86300</v>
       </c>
       <c r="M18" t="n">
-        <v>18330</v>
+        <v>83500</v>
       </c>
       <c r="N18" t="n">
-        <v>10.53</v>
+        <v>23.45</v>
       </c>
       <c r="O18" t="n">
-        <v>43343941735</v>
+        <v>116807201750</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-204000</v>
+        <v>-137000</v>
       </c>
       <c r="S18" t="n">
-        <v>-37000</v>
+        <v>-5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 대차 해지 운동 촉구. 대형 계약 임박 및 공매도 세력 관련 언급.</t>
+          <t>웨스팅하우스 지분 인수 관련 기대감 속 공매도 공방 및 단기 변동성 예상.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '대차 해지', '공매도']</t>
+          <t>['웨스팅하우스', '공매도', '지분인수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>84100</v>
+        <v>31600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>-0.34</v>
       </c>
       <c r="E19" t="n">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="F19" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G19" t="n">
-        <v>738</v>
+        <v>1096</v>
       </c>
       <c r="H19" t="n">
-        <v>23.37</v>
+        <v>17.16</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>86200</v>
+        <v>32450</v>
       </c>
       <c r="K19" t="n">
-        <v>86200</v>
+        <v>32850</v>
       </c>
       <c r="L19" t="n">
-        <v>86300</v>
+        <v>32850</v>
       </c>
       <c r="M19" t="n">
-        <v>83500</v>
+        <v>30900</v>
       </c>
       <c r="N19" t="n">
-        <v>23.45</v>
+        <v>17.5</v>
       </c>
       <c r="O19" t="n">
-        <v>114414964050</v>
+        <v>8364194350</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R19" t="n">
-        <v>-137000</v>
+        <v>-71000</v>
       </c>
       <c r="S19" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 기대감 속 공매도 공방 및 단기 변동성 예상.</t>
+          <t>유럽 담관암 신약 신청 관련 불확실성 속 FDA 실패 가능성 제기. 과거 신약 실패 경험과 공모주 청약 시점의 유럽 신청에 대한 의구심이 공존.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '공매도', '지분인수']</t>
+          <t>['담관암', 'FDA', '신약 신청']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31650</v>
+        <v>5090</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.34</v>
+        <v>-1.39</v>
       </c>
       <c r="E20" t="n">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>1085</v>
+        <v>166</v>
       </c>
       <c r="H20" t="n">
-        <v>17.16</v>
+        <v>1.29</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,47 +2251,47 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>32450</v>
+        <v>5230</v>
       </c>
       <c r="K20" t="n">
-        <v>32850</v>
+        <v>5750</v>
       </c>
       <c r="L20" t="n">
-        <v>32850</v>
+        <v>5880</v>
       </c>
       <c r="M20" t="n">
-        <v>30900</v>
+        <v>5020</v>
       </c>
       <c r="N20" t="n">
-        <v>17.5</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
-        <v>8302619275</v>
+        <v>61315925245</v>
       </c>
       <c r="P20" t="n">
-        <v>69200</v>
+        <v>8980</v>
       </c>
       <c r="Q20" t="n">
-        <v>24150</v>
+        <v>2795</v>
       </c>
       <c r="R20" t="n">
-        <v>-71000</v>
+        <v>308000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>유럽 담관암 신약 신청 관련 불확실성 속 FDA 실패 가능성 제기. 과거 신약 실패 경험과 공모주 청약 시점의 유럽 신청에 대한 의구심이 공존.</t>
+          <t>미국 보안주 강세와 삼성과의 계약 언급. 다만, 허매수 및 매도세에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA', '신약 신청']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17050</v>
+        <v>17040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F21" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G21" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H21" t="n">
         <v>0.45</v>
@@ -2358,7 +2358,7 @@
         <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>156127194740</v>
+        <v>156446969455</v>
       </c>
       <c r="P21" t="n">
         <v>30550</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 속 상용화 및 매출 발생 기대감. 개미 털기 의혹 제기.</t>
+          <t>미국 보안주 강세 속에서 주가 하락에 대한 불만과 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보안주', '상용화', '개미털기']</t>
+          <t>['보안주', '개미털기', '주가조작']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5900</v>
+        <v>14010</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.50%</t>
+          <t>'-6.48%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>533</v>
       </c>
       <c r="H22" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K22" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L22" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M22" t="n">
-        <v>5630</v>
+        <v>13520</v>
       </c>
       <c r="N22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>40665070720</v>
+        <v>32001664375</v>
       </c>
       <c r="P22" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q22" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R22" t="n">
-        <v>389000</v>
+        <v>-11000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
+          <t>국제유가 상승 및 중동 지역 긴장 고조에도 불구하고 주가 하락에 대한 의문.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['클래리티법', '공매도', '외국인']</t>
+          <t>['국제유가', '에너지주', '급락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14000</v>
+        <v>5870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-6.97%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>225</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>502</v>
+        <v>173</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14980</v>
+        <v>6310</v>
       </c>
       <c r="K23" t="n">
-        <v>15300</v>
+        <v>6390</v>
       </c>
       <c r="L23" t="n">
-        <v>15580</v>
+        <v>6450</v>
       </c>
       <c r="M23" t="n">
-        <v>13520</v>
+        <v>5630</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>31755314665</v>
+        <v>40953863625</v>
       </c>
       <c r="P23" t="n">
-        <v>36200</v>
+        <v>11370</v>
       </c>
       <c r="Q23" t="n">
-        <v>8920</v>
+        <v>3300</v>
       </c>
       <c r="R23" t="n">
-        <v>-11000</v>
+        <v>389000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">국제 유가 상승 및 지정학적 리스크에도 불구하고 흥구석유 주가 하락. 에너지주 전반의 약세 및 비축유 방출 우려.  </t>
+          <t xml:space="preserve">미국 클래리티 법안 부결 소식에 따른 가상자산 관련주 관심 증폭. 공매도 거래량 및 외국인 순매수 데이터 혼재. 향후 주가 추세에 대한 엇갈린 전망.  </t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '비축유']</t>
+          <t>['클래리티법', '공매도', '외국인']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
